--- a/plantillas/plantilla_vulnerabilidades.xlsx
+++ b/plantillas/plantilla_vulnerabilidades.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -460,8 +460,9 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,10 +523,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Veces en Retest</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Informe Pentest</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
@@ -585,12 +591,15 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Pentest Q1 2024</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>CyberSec Corp</t>
         </is>
@@ -636,7 +645,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Para Re Test</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -649,13 +658,20 @@
           <t>2024-02-28</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Pentest Q1 2024</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>CyberSec Corp</t>
         </is>
@@ -719,19 +735,22 @@
           <t>Corregido</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Pentest Móvil 2024</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SecureTest</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Por favor selecciona: Critica, Alta, Media o Baja" type="list">
       <formula1>"Critica,Alta,Media,Baja"</formula1>
     </dataValidation>
@@ -740,6 +759,9 @@
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Por favor selecciona un resultado válido" type="list">
       <formula1>"Corregido,Pendiente,Impedimento,Vulnerable,Desestimado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Debe ser un número entero &gt;= 0" type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -752,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -849,171 +871,171 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Veces en Retest: Número de veces que se ha realizado retest</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>3. VALORES PERMITIDOS:</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   SEVERIDAD:</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Critica (rojo)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Alta (naranja)</t>
+          <t xml:space="preserve">   - Critica (rojo)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Media (amarillo)</t>
+          <t xml:space="preserve">   - Alta (naranja)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Media (amarillo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">   - Baja (verde)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   ESTATUS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Pendiente</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - En Proceso</t>
+          <t xml:space="preserve">   - Pendiente</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Corregido</t>
+          <t xml:space="preserve">   - En Proceso</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Cerrado</t>
+          <t xml:space="preserve">   - Corregido</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Para Re Test</t>
+          <t xml:space="preserve">   - Cerrado</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Para Re Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t xml:space="preserve">   - Desestimado</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   RESULTADO RE TEST:</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Corregido</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Pendiente</t>
+          <t xml:space="preserve">   - Corregido</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Impedimento</t>
+          <t xml:space="preserve">   - Pendiente</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Vulnerable</t>
+          <t xml:space="preserve">   - Impedimento</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t xml:space="preserve">   - Vulnerable</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t xml:space="preserve">   - Desestimado</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>4. FORMATO DE FECHAS:</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - YYYY-MM-DD (recomendado): 2024-01-15</t>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   VECES EN RETEST:</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - DD/MM/YYYY: 15/01/2024</t>
+          <t xml:space="preserve">   - Número entero &gt;= 0 (ej: 0, 1, 2, 3...)</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1045,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5. MÚLTIPLES APLICACIONES:</t>
+          <t>4. FORMATO DE FECHAS:</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Separar con coma: 'Portal Web, API, App Móvil'</t>
+          <t xml:space="preserve">   - YYYY-MM-DD (recomendado): 2024-01-15</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - DD/MM/YYYY: 15/01/2024</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>6. AUTO-CREACIÓN DE CATÁLOGOS:</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Si una Institución, Aplicación, Proveedor o Informe no existe,</t>
+          <t>5. MÚLTIPLES APLICACIONES:</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">   el sistema lo creará automáticamente al importar.</t>
+          <t xml:space="preserve">   Separar con coma: 'Portal Web, API, App Móvil'</t>
         </is>
       </c>
     </row>
@@ -1064,26 +1086,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7. NOTAS:</t>
+          <t>6. AUTO-CREACIÓN DE CATÁLOGOS:</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Eliminar las filas de ejemplo antes de importar</t>
+          <t xml:space="preserve">   Si una Institución, Aplicación, Proveedor o Informe no existe,</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t xml:space="preserve">   el sistema lo creará automáticamente al importar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7. NOTAS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Eliminar las filas de ejemplo antes de importar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t xml:space="preserve">   - La hoja debe llamarse 'Consolidado'</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Mantener los encabezados en la fila 1</t>
         </is>

--- a/plantillas/plantilla_vulnerabilidades.xlsx
+++ b/plantillas/plantilla_vulnerabilidades.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Consolidado" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,34 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F46E5"/>
-        <bgColor rgb="004F46E5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,26 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,692 +413,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Fecha Hallazgo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Institución</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Aplicaciones</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Vulnerabilidad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Descripción del Riesgo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Recomendaciones</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Severidad</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Estatus</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Fecha Compromiso</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Resultado Re Test</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Veces en Retest</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Informe Pentest</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VULN-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Banco Central</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Portal Web Clientes</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>SQL Injection en formulario de login</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Se detectó una vulnerabilidad de inyección SQL en el formulario de autenticación que permite a un atacante ejecutar consultas arbitrarias en la base de datos.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1. Implementar consultas parametrizadas
 2. Validar y sanitizar todas las entradas de usuario
 3. Usar un WAF como capa adicional de protección</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Critica</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Juan Pérez</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2024-02-15</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Pentest Q1 2024</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>CyberSec Corp</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Banco Central</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>API Móvil</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Tokens JWT sin expiración</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Los tokens de autenticación JWT no tienen tiempo de expiración configurado, lo que permite acceso indefinido si un token es comprometido.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1. Configurar expiración de tokens (máximo 24 horas)
 2. Implementar refresh tokens
 3. Mantener lista negra de tokens revocados</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Para Re Test</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>María García</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2024-02-28</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Pentest Q1 2024</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>CyberSec Corp</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
         <is>
           <t>2024-01-20</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Fintech ABC</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>App Móvil Android</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Almacenamiento inseguro de credenciales</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>La aplicación almacena las credenciales del usuario en texto plano en SharedPreferences, accesible mediante root o backup.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1. Usar Android Keystore para almacenar datos sensibles
 2. Implementar cifrado AES-256 para datos en reposo
 3. Deshabilitar backups de la aplicación</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Corregido</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Carlos López</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2024-02-10</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Corregido</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Pentest Móvil 2024</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>SecureTest</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Por favor selecciona: Critica, Alta, Media o Baja" type="list">
-      <formula1>"Critica,Alta,Media,Baja"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Por favor selecciona un estatus válido" type="list">
-      <formula1>"Pendiente,En Proceso,Corregido,Cerrado,Para Re Test,Desestimado"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Por favor selecciona un resultado válido" type="list">
-      <formula1>"Corregido,Pendiente,Impedimento,Vulnerable,Desestimado"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Debe ser un número entero &gt;= 0" type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUCCIONES DE USO DE LA PLANTILLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1. CAMPOS OBLIGATORIOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Vulnerabilidad: Título descriptivo de la vulnerabilidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Severidad: Seleccionar de la lista (Critica, Alta, Media, Baja)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2. CAMPOS RECOMENDADOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Fecha Hallazgo: Cuándo se descubrió (YYYY-MM-DD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Institución: Empresa o cliente afectado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Aplicaciones: Sistema(s) afectado(s), separar múltiples con coma</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Descripción del Riesgo: Explicación detallada</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Recomendaciones: Pasos para remediar</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Estatus: Estado actual de la vulnerabilidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Responsable: Persona asignada para remediar</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Veces en Retest: Número de veces que se ha realizado retest</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3. VALORES PERMITIDOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   SEVERIDAD:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Critica (rojo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Alta (naranja)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Media (amarillo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Baja (verde)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ESTATUS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - En Proceso</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Corregido</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Cerrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Para Re Test</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Desestimado</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   RESULTADO RE TEST:</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Corregido</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Impedimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Vulnerable</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Desestimado</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   VECES EN RETEST:</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Número entero &gt;= 0 (ej: 0, 1, 2, 3...)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>4. FORMATO DE FECHAS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - YYYY-MM-DD (recomendado): 2024-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - DD/MM/YYYY: 15/01/2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>5. MÚLTIPLES APLICACIONES:</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Separar con coma: 'Portal Web, API, App Móvil'</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>6. AUTO-CREACIÓN DE CATÁLOGOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Si una Institución, Aplicación, Proveedor o Informe no existe,</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   el sistema lo creará automáticamente al importar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>7. NOTAS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Eliminar las filas de ejemplo antes de importar</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - La hoja debe llamarse 'Consolidado'</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - Mantener los encabezados en la fila 1</t>
         </is>
       </c>
     </row>
